--- a/诊断调查表.xlsx
+++ b/诊断调查表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375" tabRatio="810" firstSheet="1" activeTab="6"/>
+    <workbookView windowWidth="27945" windowHeight="12375" tabRatio="810" firstSheet="3" activeTab="12"/>
   </bookViews>
   <sheets>
     <sheet name="封面（竖版）" sheetId="16" r:id="rId1"/>
@@ -22115,9 +22115,36 @@
       <charset val="134"/>
     </font>
     <font>
-      <vertAlign val="superscript"/>
+      <b/>
+      <sz val="10"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
       <sz val="12"/>
+      <color indexed="10"/>
       <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <strike/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <strike/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -22137,53 +22164,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="16"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <vertAlign val="superscript"/>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <strike/>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <i/>
-      <vertAlign val="superscript"/>
-      <sz val="12"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <i/>
-      <sz val="12"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <strike/>
       <sz val="8"/>
       <color rgb="FFFF0000"/>
@@ -22198,26 +22178,46 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
+      <vertAlign val="superscript"/>
       <sz val="12"/>
-      <color indexed="10"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <strike/>
-      <sz val="10"/>
-      <color theme="1"/>
       <name val="Arial"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
+      <i/>
+      <sz val="12"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <vertAlign val="superscript"/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <vertAlign val="superscript"/>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
